--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260714.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260714.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>33,804</t>
+          <t>33,396</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.80%</t>
+          <t>10.86%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>81,710</t>
+          <t>80,723</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.08%</t>
+          <t>10.23%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>94,251</t>
+          <t>93,113</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.83%</t>
+          <t>8.62%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>37,100</t>
+          <t>36,652</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.35%</t>
+          <t>7.39%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>203,636</t>
+          <t>201,179</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.51%</t>
+          <t>5.49%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>108,302</t>
+          <t>106,995</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.12%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>51,124</t>
+          <t>50,507</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.75%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>117,458</t>
+          <t>116,040</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.40%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>61,521</t>
+          <t>60,779</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>20,221</t>
+          <t>19,977</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>122,171</t>
+          <t>120,697</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>56,584</t>
+          <t>55,901</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>142,224</t>
+          <t>140,507</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>23,510</t>
+          <t>23,227</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>25,360</t>
+          <t>25,054</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>65,010</t>
+          <t>64,226</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>11,830</t>
+          <t>11,687</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>38,378</t>
+          <t>37,915</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>51,898</t>
+          <t>51,271</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
@@ -1029,34 +1029,34 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>53,435</t>
+          <t>52,790</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>52,236</t>
+          <t>79,378</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1073,78 +1073,78 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>33,923</t>
+          <t>33,514</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>80,347</t>
+          <t>51,605</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>31,768</t>
+          <t>22,945</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>23,226</t>
+          <t>31,384</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>49,071</t>
+          <t>48,479</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>28,767</t>
+          <t>28,420</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1205,100 +1205,100 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>21,609</t>
+          <t>21,348</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>99,194</t>
+          <t>5,073</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>5,135</t>
+          <t>97,997</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>78,337</t>
+          <t>9,282</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,396</t>
+          <t>77,391</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>13,828</t>
+          <t>13,661</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>31,632</t>
+          <t>31,250</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>152,287</t>
+          <t>150,449</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>11,109</t>
+          <t>10,975</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>32,025</t>
+          <t>31,638</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>26,901</t>
+          <t>26,577</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>45,373</t>
+          <t>44,825</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>14,007</t>
+          <t>13,838</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>16,828</t>
+          <t>16,625</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1535,56 +1535,56 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>7,124</t>
+          <t>7,038</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MYRG US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>MYR集團公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>3,810</t>
+          <t>6,059</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>MYRG US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>MYR集團公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>6,133</t>
+          <t>3,764</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>98,609</t>
+          <t>97,418</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>24,541</t>
+          <t>24,245</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,963</t>
+          <t>2,927</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,370</t>
+          <t>8,269</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>19,254</t>
+          <t>19,022</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>39,924</t>
+          <t>39,442</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>177,793,560</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
